--- a/outputs/48080.xlsx
+++ b/outputs/48080.xlsx
@@ -118,16 +118,20 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -384,70 +388,70 @@
   <dimension ref="A1:C89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.21"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="0" t="n">
-        <f aca="true">OFFSET($A$1, (ROW()-2)*16+24, 0)</f>
+      <c r="C2" s="1" t="n">
+        <f aca="true">OFFSET($A$25,(ROW()-2)*16,0)</f>
         <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="n">
-        <f aca="true">OFFSET($A$1, (ROW()-2)*16+24, 0)</f>
+      <c r="C3" s="1" t="n">
+        <f aca="true">OFFSET($A$25,(ROW()-2)*16,0)</f>
         <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="n">
-        <f aca="true">OFFSET($A$1, (ROW()-2)*16+24, 0)</f>
+      <c r="C4" s="1" t="n">
+        <f aca="true">OFFSET($A$25,(ROW()-2)*16,0)</f>
         <v>87</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="n">
-        <f aca="true">OFFSET($A$1, (ROW()-2)*16+24, 0)</f>
+      <c r="C5" s="1" t="n">
+        <f aca="true">OFFSET($A$25,(ROW()-2)*16,0)</f>
         <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="n">
-        <f aca="true">OFFSET($A$1, (ROW()-2)*16+24, 0)</f>
+      <c r="C6" s="1" t="n">
+        <f aca="true">OFFSET($A$25,(ROW()-2)*16,0)</f>
         <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="1" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
+      <c r="A57" s="1" t="n">
         <v>87</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="n">
+      <c r="A73" s="1" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="n">
+      <c r="A89" s="1" t="n">
         <v>6</v>
       </c>
     </row>

--- a/outputs/48080.xlsx
+++ b/outputs/48080.xlsx
@@ -402,31 +402,31 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="1" t="n">
-        <f aca="true">OFFSET($A$25,(ROW()-2)*16,0)</f>
+        <f aca="false">A25</f>
         <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="1" t="n">
-        <f aca="true">OFFSET($A$25,(ROW()-2)*16,0)</f>
+        <f aca="false">A41</f>
         <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="n">
-        <f aca="true">OFFSET($A$25,(ROW()-2)*16,0)</f>
+        <f aca="false">A57</f>
         <v>87</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="n">
-        <f aca="true">OFFSET($A$25,(ROW()-2)*16,0)</f>
+        <f aca="false">A73</f>
         <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="1" t="n">
-        <f aca="true">OFFSET($A$25,(ROW()-2)*16,0)</f>
+        <f aca="false">A89</f>
         <v>6</v>
       </c>
     </row>
